--- a/brunei/FINAL_PANEL.xlsx
+++ b/brunei/FINAL_PANEL.xlsx
@@ -625,7 +625,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
@@ -4952,7 +4952,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T46" t="inlineStr"/>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T48" t="inlineStr"/>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
@@ -5589,7 +5589,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T54" t="inlineStr"/>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T55" t="inlineStr"/>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T56" t="inlineStr"/>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T57" t="inlineStr"/>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T58" t="inlineStr"/>
@@ -6214,7 +6214,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T59" t="inlineStr"/>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T60" t="inlineStr"/>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T61" t="inlineStr"/>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T62" t="inlineStr"/>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T63" t="inlineStr"/>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T64" t="inlineStr"/>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T65" t="inlineStr"/>
@@ -6815,7 +6815,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T66" t="inlineStr"/>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T67" t="inlineStr"/>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T68" t="inlineStr"/>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="T69" t="inlineStr"/>
@@ -9505,7 +9505,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -9895,7 +9895,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -10039,7 +10039,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -10417,7 +10417,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -10495,7 +10495,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -10729,7 +10729,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -10885,7 +10885,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -10963,7 +10963,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -11119,7 +11119,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -11197,7 +11197,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -11353,7 +11353,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -11587,7 +11587,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -11821,7 +11821,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -12043,7 +12043,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -12187,7 +12187,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -12343,7 +12343,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -12421,7 +12421,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -12487,7 +12487,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -12553,7 +12553,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -12709,7 +12709,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -12783,7 +12783,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P45" t="inlineStr"/>
@@ -12853,7 +12853,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P46" t="inlineStr"/>
@@ -12923,7 +12923,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
@@ -12993,7 +12993,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P48" t="inlineStr"/>
@@ -13063,7 +13063,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P49" t="inlineStr"/>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P50" t="inlineStr"/>
@@ -13203,7 +13203,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P51" t="inlineStr"/>
@@ -13273,7 +13273,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P52" t="inlineStr"/>
@@ -13343,7 +13343,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P53" t="inlineStr"/>
@@ -13413,7 +13413,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P54" t="inlineStr"/>
@@ -13483,7 +13483,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P55" t="inlineStr"/>
@@ -13553,7 +13553,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P56" t="inlineStr"/>
@@ -13623,7 +13623,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P57" t="inlineStr"/>
@@ -13693,7 +13693,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P58" t="inlineStr"/>
@@ -13751,7 +13751,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P59" t="inlineStr"/>
@@ -13809,7 +13809,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P60" t="inlineStr"/>
@@ -13867,7 +13867,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P61" t="inlineStr"/>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P62" t="inlineStr"/>
@@ -14007,7 +14007,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P63" t="inlineStr"/>
@@ -14077,7 +14077,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P64" t="inlineStr"/>
@@ -14135,7 +14135,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P65" t="inlineStr"/>
@@ -14205,7 +14205,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P66" t="inlineStr"/>
@@ -14263,7 +14263,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P67" t="inlineStr"/>
@@ -14321,7 +14321,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P68" t="inlineStr"/>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="P69" t="inlineStr"/>
@@ -18092,7 +18092,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
     </row>
@@ -18125,7 +18125,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
     </row>
@@ -18158,7 +18158,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
     </row>
@@ -18191,7 +18191,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
     </row>
@@ -18224,7 +18224,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
     </row>
@@ -18257,7 +18257,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
     </row>
@@ -18290,7 +18290,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
     </row>
@@ -18323,7 +18323,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
     </row>
@@ -18356,7 +18356,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
     </row>
@@ -18389,7 +18389,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
     </row>
@@ -19412,7 +19412,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -19487,7 +19487,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -19562,7 +19562,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -19637,7 +19637,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -19712,7 +19712,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -19787,7 +19787,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -19937,7 +19937,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -20087,7 +20087,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -20162,7 +20162,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -20237,7 +20237,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -20312,7 +20312,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -20387,7 +20387,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -20462,7 +20462,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -20537,7 +20537,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -20612,7 +20612,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -20687,7 +20687,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -20762,7 +20762,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -20837,7 +20837,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -20912,7 +20912,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -20987,7 +20987,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -21062,7 +21062,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -21137,7 +21137,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -21212,7 +21212,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -21287,7 +21287,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -21362,7 +21362,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -21437,7 +21437,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -21512,7 +21512,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -21587,7 +21587,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -21662,7 +21662,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -21732,7 +21732,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -21802,7 +21802,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -21877,7 +21877,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -21947,7 +21947,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -22017,7 +22017,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -22092,7 +22092,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -22167,7 +22167,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -22237,7 +22237,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -22312,7 +22312,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -22387,7 +22387,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -22462,7 +22462,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -22537,7 +22537,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -22612,7 +22612,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -22687,7 +22687,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -22762,7 +22762,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -22832,7 +22832,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -22897,7 +22897,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -22962,7 +22962,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -23037,7 +23037,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -23112,7 +23112,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -23187,7 +23187,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -23262,7 +23262,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -23337,7 +23337,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -23487,7 +23487,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -23562,7 +23562,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -23637,7 +23637,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -23712,7 +23712,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -23787,7 +23787,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -23862,7 +23862,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -23937,7 +23937,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -24012,7 +24012,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -24087,7 +24087,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -24198,7 +24198,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -24246,7 +24246,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -24294,7 +24294,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -24342,7 +24342,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -24390,7 +24390,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -24438,7 +24438,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -24486,7 +24486,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -24534,7 +24534,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -24582,7 +24582,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -24630,7 +24630,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -24678,7 +24678,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -24726,7 +24726,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -24774,7 +24774,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -24822,7 +24822,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -24870,7 +24870,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -24918,7 +24918,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -24966,7 +24966,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -25014,7 +25014,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -25062,7 +25062,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -25110,7 +25110,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -25158,7 +25158,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -25206,7 +25206,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -25254,7 +25254,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -25302,7 +25302,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -25350,7 +25350,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -25398,7 +25398,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -25446,7 +25446,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -25542,7 +25542,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -25590,7 +25590,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -25638,7 +25638,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -25686,7 +25686,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -25734,7 +25734,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -25782,7 +25782,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -25830,7 +25830,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -25878,7 +25878,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -25926,7 +25926,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -25974,7 +25974,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -26022,7 +26022,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>million Brunei dollars</t>
+          <t>BND million</t>
         </is>
       </c>
       <c r="H40" t="n">

--- a/brunei/FINAL_PANEL.xlsx
+++ b/brunei/FINAL_PANEL.xlsx
@@ -9508,11 +9508,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Development of school and higher education institution infrastructure under the 12th National Development Plan; Focus projects to support the budget focus areas for Financial Year 2024/2025; MPEC programmes: i-Ready, TVET Scheme, Skillsplus, SPIN in Accountancy and Tradeskills; Miftaahun Najaah Scheme; Research and innovation allocations under the 12th National Development Plan; Research costs for public higher education institutions; Scholarships through the Ministry of Education and the Ministry of Religious Affairs</t>
-        </is>
-      </c>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9586,11 +9582,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Development of school and higher education institution infrastructure under the 12th National Development Plan; Focus projects to support the budget focus areas for Financial Year 2024/2025</t>
-        </is>
-      </c>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9664,11 +9656,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Electricity supply projects under the 12th National Development Plan; Green Building initiatives under the 12th National Development Plan</t>
-        </is>
-      </c>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9742,11 +9730,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Electricity supply projects under the 12th National Development Plan</t>
-        </is>
-      </c>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9820,11 +9804,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>National housing provision projects under the 12th National Development Plan</t>
-        </is>
-      </c>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9898,11 +9878,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Water supply and sewerage system upgrading projects under the 12th National Development Plan</t>
-        </is>
-      </c>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9976,11 +9952,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Medical and health infrastructure development under the 12th National Development Plan</t>
-        </is>
-      </c>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10042,11 +10014,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Payment for medical treatment services at Gleneagles Jerudong Park Medical Centre, Brunei Cancer Centre and Brunei Neuroscience, Stroke and Rehabilitation Centre</t>
-        </is>
-      </c>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10120,11 +10088,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>IT Central Procurement projects and software licences for all ministries and government departments</t>
-        </is>
-      </c>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10198,11 +10162,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Aquaculture industry site development and basic infrastructure projects; Infrastructure provision for enhancement of the agricultural industry nationwide - Phase 2; Livestock industry development plan; Preparation and upgrading works for infrastructure and basic facilities in existing and new agricultural development areas</t>
-        </is>
-      </c>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -10276,11 +10236,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Infrastructure provision for enhancement of the agricultural industry nationwide - Phase 2; Preparation and upgrading works for infrastructure and basic facilities in existing and new agricultural development areas</t>
-        </is>
-      </c>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -10354,11 +10310,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Focus projects to support the budget focus areas for Financial Year 2024/2025; Research and innovation allocations under the 12th National Development Plan</t>
-        </is>
-      </c>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -10420,11 +10372,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Purchase of medicines, medical consumables and laboratory testing needs</t>
-        </is>
-      </c>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -10498,11 +10446,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Bru-HIMS 2.0 system project; Maintenance of Bru-HIMS and enhancement of BruHealth system features</t>
-        </is>
-      </c>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10576,11 +10520,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Capacity enhancement programme for irrigation systems in agricultural development areas nationwide - Phase 2; Preparation and upgrading works for infrastructure and basic facilities in existing and new agricultural development areas</t>
-        </is>
-      </c>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -10654,11 +10594,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Focus projects to support the budget focus areas for Financial Year 2024/2025; Scholarships through the Ministry of Education and the Ministry of Religious Affairs</t>
-        </is>
-      </c>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10732,11 +10668,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Flood prevention projects under the 12th National Development Plan</t>
-        </is>
-      </c>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10810,11 +10742,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Airport infrastructure modernisation projects under the 12th National Development Plan</t>
-        </is>
-      </c>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -10888,11 +10816,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Education digital infrastructure and smart systems under the 12th National Development Plan; Focus projects to support the budget focus areas for Financial Year 2024/2025</t>
-        </is>
-      </c>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -10966,11 +10890,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Focus projects to support the budget focus areas for Financial Year 2024/2025; MPEC programmes: i-Ready, TVET Scheme, Skillsplus, SPIN in Accountancy and Tradeskills</t>
-        </is>
-      </c>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -11044,11 +10964,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Education information and data management systems under the 12th National Development Plan; Focus projects to support the budget focus areas for Financial Year 2024/2025</t>
-        </is>
-      </c>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -11122,11 +11038,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Management of infectious disease crises and assistance to affected individuals or communities</t>
-        </is>
-      </c>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -11200,11 +11112,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Government digital transformation projects under the 12th National Development Plan</t>
-        </is>
-      </c>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -11278,11 +11186,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Tourism product improvement projects under the 12th National Development Plan</t>
-        </is>
-      </c>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -11356,11 +11260,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Integrated government databases and asset management systems under the 12th National Development Plan</t>
-        </is>
-      </c>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -11434,11 +11334,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Focus projects to support the budget focus areas for Financial Year 2024/2025; Miftaahun Najaah Scheme</t>
-        </is>
-      </c>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -11512,11 +11408,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>High-technology vegetable production enhancement programme under the 12th National Development Plan; Preparation and upgrading works for infrastructure and basic facilities in existing and new agricultural development areas</t>
-        </is>
-      </c>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -11590,11 +11482,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Focus projects to support the budget focus areas for Financial Year 2024/2025</t>
-        </is>
-      </c>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -11668,11 +11556,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Focus projects to support the budget focus areas for Financial Year 2024/2025</t>
-        </is>
-      </c>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -11746,11 +11630,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Focus projects to support the budget focus areas for Financial Year 2024/2025</t>
-        </is>
-      </c>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -11824,11 +11704,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Quality health service support provision</t>
-        </is>
-      </c>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -11902,11 +11778,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Maintenance of Bru-HIMS and enhancement of BruHealth system features</t>
-        </is>
-      </c>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -11980,11 +11852,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Natural disaster management</t>
-        </is>
-      </c>
+      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -12046,11 +11914,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Judiciary digital case management systems under the 12th National Development Plan</t>
-        </is>
-      </c>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -12112,11 +11976,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Aquaculture industry site development and basic infrastructure projects</t>
-        </is>
-      </c>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -12190,11 +12050,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Livestock industry development plan</t>
-        </is>
-      </c>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -12268,11 +12124,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Environmental sustainability, reforestation and forest conservation programmes under the 12th National Development Plan</t>
-        </is>
-      </c>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -12346,11 +12198,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Digital transformation in the transport and logistics sector under the 12th National Development Plan</t>
-        </is>
-      </c>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -12424,11 +12272,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Migration from TAFIS 1.0 to TAFIS 2.0</t>
-        </is>
-      </c>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -12490,11 +12334,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Preparation and upgrading works for infrastructure and basic facilities in existing and new agricultural development areas</t>
-        </is>
-      </c>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -12556,11 +12396,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Paddy buy-back scheme and purchase of hybrid paddy seeds</t>
-        </is>
-      </c>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -12634,11 +12470,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Research costs for public higher education institutions</t>
-        </is>
-      </c>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -12712,11 +12544,7 @@
           <t>BND million</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>National Adaptation Plan for Climate Change under the 12th National Development Plan</t>
-        </is>
-      </c>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">

--- a/brunei/FINAL_PANEL.xlsx
+++ b/brunei/FINAL_PANEL.xlsx
@@ -9157,7 +9157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9178,20 +9178,30 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>printed_total</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>total_basis</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>matched_amount</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>coverage_pct</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>programs_matched</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>programs_total</t>
         </is>
@@ -9209,18 +9219,26 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>1949.8</v>
+      </c>
+      <c r="D2" t="n">
         <v>1949.77</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>printed</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>1627.3</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>83.5</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>18</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>22</v>
       </c>
     </row>
@@ -9236,18 +9254,26 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>493.8</v>
+      </c>
+      <c r="D3" t="n">
         <v>493.77</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>printed</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>349.1</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>70.7</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>11</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>12</v>
       </c>
     </row>
@@ -9266,15 +9292,23 @@
         <v>624.9</v>
       </c>
       <c r="D4" t="n">
+        <v>624.9</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>printed</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>596.9</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>95.5</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>5</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>7</v>
       </c>
     </row>
@@ -22472,7 +22506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22493,10 +22527,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>printed_total</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>total_basis</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>matched_distinct</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
@@ -22514,12 +22558,20 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>1949.8</v>
+      </c>
+      <c r="D2" t="n">
         <v>1949.77</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>printed</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>1627.3</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -22537,12 +22589,20 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>493.8</v>
+      </c>
+      <c r="D3" t="n">
         <v>493.77</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>printed</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>349.1</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -22563,9 +22623,17 @@
         <v>624.9</v>
       </c>
       <c r="D4" t="n">
+        <v>624.9</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>printed</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>596.9</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
